--- a/data/trans_bre/P26-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P26-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 18,26</t>
+          <t>-0,36; 17,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 12,47</t>
+          <t>-4,83; 12,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 12,86</t>
+          <t>-3,64; 12,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 12,63</t>
+          <t>-4,48; 11,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 63,6</t>
+          <t>-1,15; 59,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 35,37</t>
+          <t>-11,05; 38,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 43,97</t>
+          <t>-10,16; 43,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 94,26</t>
+          <t>-20,25; 76,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 14,3</t>
+          <t>1,91; 14,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 14,86</t>
+          <t>2,52; 15,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 15,15</t>
+          <t>4,02; 15,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 7,7</t>
+          <t>-2,47; 7,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 64,36</t>
+          <t>6,38; 62,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 50,62</t>
+          <t>6,95; 49,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 73,76</t>
+          <t>16,2; 76,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 117,61</t>
+          <t>-19,34; 112,86</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 18,86</t>
+          <t>3,53; 18,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 7,83</t>
+          <t>-6,88; 8,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 0,67</t>
+          <t>-10,12; 0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,19</t>
+          <t>4,89; 13,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 77,89</t>
+          <t>11,17; 78,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 24,64</t>
+          <t>-17,06; 26,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 4,31</t>
+          <t>-49,7; 5,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,65; 281,23</t>
+          <t>58,3; 278,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 20,36</t>
+          <t>5,79; 20,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 6,99</t>
+          <t>-6,43; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,44</t>
+          <t>-6,56; 7,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 1,71</t>
+          <t>-14,25; 1,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 81,8</t>
+          <t>17,14; 79,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 27,81</t>
+          <t>-19,59; 27,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 31,1</t>
+          <t>-20,54; 31,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 13,59</t>
+          <t>-66,62; 19,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 11,42</t>
+          <t>-7,96; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 16,86</t>
+          <t>-1,94; 16,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 2,8</t>
+          <t>-14,01; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,73</t>
+          <t>-2,13; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 47,95</t>
+          <t>-23,93; 48,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 60,92</t>
+          <t>-5,04; 59,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 13,99</t>
+          <t>-43,39; 17,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 277,25</t>
+          <t>-33,66; 297,92</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 20,31</t>
+          <t>2,25; 18,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 22,54</t>
+          <t>4,41; 21,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 14,96</t>
+          <t>-1,79; 14,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,8</t>
+          <t>-4,18; 5,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,16; 87,49</t>
+          <t>6,89; 76,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,28; 86,51</t>
+          <t>12,92; 84,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 74,87</t>
+          <t>-6,64; 71,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,88; 70,5</t>
+          <t>-30,79; 71,5</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 13,05</t>
+          <t>2,39; 13,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,66</t>
+          <t>1,87; 13,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,17</t>
+          <t>-1,96; 8,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 5,93</t>
+          <t>-12,95; 6,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 48,61</t>
+          <t>6,79; 48,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 44,41</t>
+          <t>5,05; 44,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 38,33</t>
+          <t>-6,05; 37,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 32,28</t>
+          <t>-57,19; 33,01</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,18</t>
+          <t>0,52; 10,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 9,55</t>
+          <t>0,46; 10,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,16</t>
+          <t>-6,98; 1,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 1,17</t>
+          <t>-62,48; 1,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 43,88</t>
+          <t>1,41; 40,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 33,13</t>
+          <t>0,92; 36,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 5,33</t>
+          <t>-27,04; 9,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-92,58; 21,77</t>
+          <t>-92,78; 24,7</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,12</t>
+          <t>6,25; 10,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,21</t>
+          <t>3,48; 8,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,66</t>
+          <t>-0,67; 3,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 1,91</t>
+          <t>-28,66; 1,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,02; 40,75</t>
+          <t>20,94; 39,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,83; 25,92</t>
+          <t>10,03; 26,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 15,11</t>
+          <t>-2,56; 15,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 16,58</t>
+          <t>-72,31; 16,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P26-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P26-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 17,63</t>
+          <t>0,17; 17,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 12,94</t>
+          <t>-4,67; 12,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 12,92</t>
+          <t>-3,63; 13,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 11,41</t>
+          <t>-2,9; 10,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 59,37</t>
+          <t>0,08; 59,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 38,04</t>
+          <t>-10,68; 37,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 43,41</t>
+          <t>-9,43; 44,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 76,08</t>
+          <t>-14,07; 79,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,19</t>
+          <t>1,9; 14,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 15,05</t>
+          <t>2,08; 14,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,5</t>
+          <t>4,3; 16,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 7,55</t>
+          <t>-1,93; 7,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 62,45</t>
+          <t>5,69; 64,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 49,37</t>
+          <t>5,69; 51,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 76,72</t>
+          <t>15,75; 79,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 112,86</t>
+          <t>-16,35; 120,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>134,03%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 18,69</t>
+          <t>3,54; 19,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 8,3</t>
+          <t>-6,8; 8,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 0,73</t>
+          <t>-10,84; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 13,39</t>
+          <t>2,45; 11,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 78,04</t>
+          <t>11,4; 84,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 26,96</t>
+          <t>-17,46; 27,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 5,27</t>
+          <t>-50,12; 8,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,3; 278,27</t>
+          <t>22,78; 212,8</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,63%</t>
+          <t>-10,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,21</t>
+          <t>6,24; 20,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 7,11</t>
+          <t>-5,97; 6,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,83</t>
+          <t>-6,43; 7,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 1,75</t>
+          <t>-9,0; 5,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 79,3</t>
+          <t>19,45; 81,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 27,59</t>
+          <t>-17,94; 27,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 31,52</t>
+          <t>-19,9; 31,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 19,4</t>
+          <t>-43,73; 59,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 11,02</t>
+          <t>-7,38; 11,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 16,12</t>
+          <t>-2,53; 16,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 3,62</t>
+          <t>-14,88; 2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,79</t>
+          <t>-3,28; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 48,35</t>
+          <t>-22,32; 48,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 59,05</t>
+          <t>-6,6; 55,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 17,69</t>
+          <t>-46,36; 10,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 297,92</t>
+          <t>-43,2; 176,11</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 18,81</t>
+          <t>2,77; 20,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 21,9</t>
+          <t>4,26; 21,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 14,0</t>
+          <t>-2,25; 13,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 5,73</t>
+          <t>-5,65; 4,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 76,49</t>
+          <t>7,89; 84,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,92; 84,24</t>
+          <t>11,28; 81,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 71,55</t>
+          <t>-8,21; 70,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 71,5</t>
+          <t>-37,83; 56,55</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-8,61%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,71</t>
+          <t>2,04; 13,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 13,78</t>
+          <t>2,07; 13,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,76</t>
+          <t>-2,01; 8,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 6,03</t>
+          <t>-1,2; 8,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 48,11</t>
+          <t>6,5; 47,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 44,21</t>
+          <t>6,22; 43,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 37,58</t>
+          <t>-6,68; 35,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 33,01</t>
+          <t>-6,09; 52,23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-26,75</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-81,48%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 10,91</t>
+          <t>1,39; 11,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 10,62</t>
+          <t>0,09; 10,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,91</t>
+          <t>-6,78; 1,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,48; 1,17</t>
+          <t>-2,55; 2,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 40,67</t>
+          <t>4,22; 43,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 36,06</t>
+          <t>-0,24; 36,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 9,5</t>
+          <t>-27,4; 8,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-92,78; 24,7</t>
+          <t>-34,42; 52,99</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,93</t>
+          <t>6,1; 11,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,32</t>
+          <t>3,44; 8,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,75</t>
+          <t>-0,47; 3,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 1,85</t>
+          <t>0,46; 3,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,94; 39,62</t>
+          <t>20,41; 39,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,19</t>
+          <t>10,35; 26,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 15,44</t>
+          <t>-2,04; 15,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 16,22</t>
+          <t>3,67; 36,2</t>
         </is>
       </c>
     </row>
